--- a/docs/examples/realistic-billing-review.xlsx
+++ b/docs/examples/realistic-billing-review.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Source lineage" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Review history" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Coverage gaps" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Follow-up" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Overview'!$1:$1</definedName>
@@ -25,6 +26,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Source lineage'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Review history'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Coverage gaps'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Follow-up'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -271,8 +273,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="ReviewhistoryData" displayName="ReviewhistoryData" ref="A1:H5" headerRowCount="1">
-  <autoFilter ref="A1:H5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="ReviewhistoryData" displayName="ReviewhistoryData" ref="A1:H18" headerRowCount="1">
+  <autoFilter ref="A1:H18"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Finding"/>
     <tableColumn id="2" name="Sequence"/>
@@ -296,6 +298,24 @@
     <tableColumn id="3" name="Coverage"/>
     <tableColumn id="4" name="Reason"/>
     <tableColumn id="5" name="Financial estimate"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="FollowupData" displayName="FollowupData" ref="A1:I10" headerRowCount="1">
+  <autoFilter ref="A1:I10"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="Case reference"/>
+    <tableColumn id="2" name="Facility"/>
+    <tableColumn id="3" name="Review basis"/>
+    <tableColumn id="4" name="Latest status"/>
+    <tableColumn id="5" name="Owner"/>
+    <tableColumn id="6" name="Correction / evidence reference"/>
+    <tableColumn id="7" name="Verified run"/>
+    <tableColumn id="8" name="Last evidence run"/>
+    <tableColumn id="9" name="Updated at"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -641,7 +661,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>RUN-a4a169d63c2f4894959f2d62eb325571</t>
+          <t>RUN-c6c77b43defc42aaa23dc71ea9270825</t>
         </is>
       </c>
     </row>
@@ -653,7 +673,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T04:46:28+00:00</t>
+          <t>2026-10-24T15:21:42+00:00</t>
         </is>
       </c>
     </row>
@@ -713,7 +733,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Current completed run</t>
+          <t>Completed run - original source evidence</t>
         </is>
       </c>
     </row>
@@ -999,7 +1019,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>75af9a99a315ce55a1a73cd061e07f647c55295f6b9db431c8e9f3fb03118629</t>
+          <t>402fe7aa026500768cb8c7d44ca7c858ac8eed757079016dd09d7849f5c7e62b</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3272,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T04:46:27.632887+00:00</t>
+          <t>2026-10-24T15:21:41.675451+00:00</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -3313,7 +3333,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T04:46:27.632887+00:00</t>
+          <t>2026-10-24T15:21:41.675451+00:00</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -3374,7 +3394,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T04:46:27.632887+00:00</t>
+          <t>2026-10-24T15:21:41.675451+00:00</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -3435,7 +3455,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T04:46:27.632887+00:00</t>
+          <t>2026-10-24T15:21:41.675451+00:00</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -3496,7 +3516,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T04:46:27.632887+00:00</t>
+          <t>2026-10-24T15:21:41.675451+00:00</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -3557,7 +3577,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T04:46:27.632887+00:00</t>
+          <t>2026-10-24T15:21:41.675451+00:00</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -3618,7 +3638,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T04:46:27.632887+00:00</t>
+          <t>2026-10-24T15:21:41.675451+00:00</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -3740,7 +3760,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>FIL-f7072af995bd4a26a9dc9444a1482242</t>
+          <t>FIL-5c41391bac9e4b249016a33dd1cbd4c9</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3795,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>FIL-f7072af995bd4a26a9dc9444a1482242</t>
+          <t>FIL-5c41391bac9e4b249016a33dd1cbd4c9</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3830,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>FIL-f7072af995bd4a26a9dc9444a1482242</t>
+          <t>FIL-5c41391bac9e4b249016a33dd1cbd4c9</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3865,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>FIL-f7072af995bd4a26a9dc9444a1482242</t>
+          <t>FIL-5c41391bac9e4b249016a33dd1cbd4c9</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3900,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>FIL-f7072af995bd4a26a9dc9444a1482242</t>
+          <t>FIL-5c41391bac9e4b249016a33dd1cbd4c9</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3935,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>FIL-f7072af995bd4a26a9dc9444a1482242</t>
+          <t>FIL-5c41391bac9e4b249016a33dd1cbd4c9</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3970,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>FIL-f7072af995bd4a26a9dc9444a1482242</t>
+          <t>FIL-5c41391bac9e4b249016a33dd1cbd4c9</t>
         </is>
       </c>
     </row>
@@ -3985,7 +4005,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>FIL-603743fa149b4ad29ae86d7e00925207</t>
+          <t>FIL-3952836487fc4e09a94ba02fd7712f19</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4040,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>FIL-603743fa149b4ad29ae86d7e00925207</t>
+          <t>FIL-3952836487fc4e09a94ba02fd7712f19</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4075,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>FIL-603743fa149b4ad29ae86d7e00925207</t>
+          <t>FIL-3952836487fc4e09a94ba02fd7712f19</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4110,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>FIL-603743fa149b4ad29ae86d7e00925207</t>
+          <t>FIL-3952836487fc4e09a94ba02fd7712f19</t>
         </is>
       </c>
     </row>
@@ -4125,7 +4145,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>FIL-603743fa149b4ad29ae86d7e00925207</t>
+          <t>FIL-3952836487fc4e09a94ba02fd7712f19</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4180,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>FIL-603743fa149b4ad29ae86d7e00925207</t>
+          <t>FIL-3952836487fc4e09a94ba02fd7712f19</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4215,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>FIL-603743fa149b4ad29ae86d7e00925207</t>
+          <t>FIL-3952836487fc4e09a94ba02fd7712f19</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4250,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>FIL-603743fa149b4ad29ae86d7e00925207</t>
+          <t>FIL-3952836487fc4e09a94ba02fd7712f19</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4285,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>FIL-603743fa149b4ad29ae86d7e00925207</t>
+          <t>FIL-3952836487fc4e09a94ba02fd7712f19</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4320,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>FIL-603743fa149b4ad29ae86d7e00925207</t>
+          <t>FIL-3952836487fc4e09a94ba02fd7712f19</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4355,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>FIL-603743fa149b4ad29ae86d7e00925207</t>
+          <t>FIL-3952836487fc4e09a94ba02fd7712f19</t>
         </is>
       </c>
     </row>
@@ -4370,7 +4390,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>FIL-603743fa149b4ad29ae86d7e00925207</t>
+          <t>FIL-3952836487fc4e09a94ba02fd7712f19</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4425,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>FIL-603743fa149b4ad29ae86d7e00925207</t>
+          <t>FIL-3952836487fc4e09a94ba02fd7712f19</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4460,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>FIL-603743fa149b4ad29ae86d7e00925207</t>
+          <t>FIL-3952836487fc4e09a94ba02fd7712f19</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4495,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>FIL-603743fa149b4ad29ae86d7e00925207</t>
+          <t>FIL-3952836487fc4e09a94ba02fd7712f19</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4530,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>FIL-603743fa149b4ad29ae86d7e00925207</t>
+          <t>FIL-3952836487fc4e09a94ba02fd7712f19</t>
         </is>
       </c>
     </row>
@@ -4545,7 +4565,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>FIL-603743fa149b4ad29ae86d7e00925207</t>
+          <t>FIL-3952836487fc4e09a94ba02fd7712f19</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4600,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>FIL-603743fa149b4ad29ae86d7e00925207</t>
+          <t>FIL-3952836487fc4e09a94ba02fd7712f19</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4635,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>FIL-7b23cab27ede45ef8fc643e784523e45</t>
+          <t>FIL-abb8be7a15994602a933e365bc84719e</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4670,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>FIL-7b23cab27ede45ef8fc643e784523e45</t>
+          <t>FIL-abb8be7a15994602a933e365bc84719e</t>
         </is>
       </c>
     </row>
@@ -4685,7 +4705,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>FIL-7b23cab27ede45ef8fc643e784523e45</t>
+          <t>FIL-abb8be7a15994602a933e365bc84719e</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4740,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>FIL-7b23cab27ede45ef8fc643e784523e45</t>
+          <t>FIL-abb8be7a15994602a933e365bc84719e</t>
         </is>
       </c>
     </row>
@@ -4755,7 +4775,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>FIL-7b23cab27ede45ef8fc643e784523e45</t>
+          <t>FIL-abb8be7a15994602a933e365bc84719e</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4810,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>FIL-7b23cab27ede45ef8fc643e784523e45</t>
+          <t>FIL-abb8be7a15994602a933e365bc84719e</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4845,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>FIL-7b23cab27ede45ef8fc643e784523e45</t>
+          <t>FIL-abb8be7a15994602a933e365bc84719e</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4880,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>FIL-7b23cab27ede45ef8fc643e784523e45</t>
+          <t>FIL-abb8be7a15994602a933e365bc84719e</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4915,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>FIL-7b23cab27ede45ef8fc643e784523e45</t>
+          <t>FIL-abb8be7a15994602a933e365bc84719e</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4950,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>FIL-7b23cab27ede45ef8fc643e784523e45</t>
+          <t>FIL-abb8be7a15994602a933e365bc84719e</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4985,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>FIL-7b23cab27ede45ef8fc643e784523e45</t>
+          <t>FIL-abb8be7a15994602a933e365bc84719e</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5020,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>FIL-7b23cab27ede45ef8fc643e784523e45</t>
+          <t>FIL-abb8be7a15994602a933e365bc84719e</t>
         </is>
       </c>
     </row>
@@ -5035,7 +5055,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>FIL-7b23cab27ede45ef8fc643e784523e45</t>
+          <t>FIL-abb8be7a15994602a933e365bc84719e</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5090,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>FIL-7b23cab27ede45ef8fc643e784523e45</t>
+          <t>FIL-abb8be7a15994602a933e365bc84719e</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5125,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>FIL-7b23cab27ede45ef8fc643e784523e45</t>
+          <t>FIL-abb8be7a15994602a933e365bc84719e</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5160,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>FIL-7b23cab27ede45ef8fc643e784523e45</t>
+          <t>FIL-abb8be7a15994602a933e365bc84719e</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5195,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>FIL-7b23cab27ede45ef8fc643e784523e45</t>
+          <t>FIL-abb8be7a15994602a933e365bc84719e</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5230,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>FIL-7b23cab27ede45ef8fc643e784523e45</t>
+          <t>FIL-abb8be7a15994602a933e365bc84719e</t>
         </is>
       </c>
     </row>
@@ -5245,7 +5265,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>FIL-7b23cab27ede45ef8fc643e784523e45</t>
+          <t>FIL-abb8be7a15994602a933e365bc84719e</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5300,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>FIL-7b23cab27ede45ef8fc643e784523e45</t>
+          <t>FIL-abb8be7a15994602a933e365bc84719e</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5383,7 +5403,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T04:46:28.052331+00:00</t>
+          <t>2026-10-24T15:21:42.116455+00:00</t>
         </is>
       </c>
       <c r="F2" s="2" t="n"/>
@@ -5394,7 +5414,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>a12449064015bc68730d2cf55cb5b1f77b1d8d1a4e8e82c9f988eca549b5947a</t>
+          <t>93ab879ebadbac54f52fd20adf67e7f95918ff26726c58541dbedf926c428e78</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5439,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T04:46:28.118812+00:00</t>
+          <t>2026-10-24T15:21:42.198589+00:00</t>
         </is>
       </c>
       <c r="F3" s="2" t="n"/>
@@ -5430,7 +5450,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>b93071f3d369d8f2f6f4ae6a15a853700d13d0c3115ca23b2835773ae2b4dcb1</t>
+          <t>b990dedd585e1ed7d547f8f0c72574f2db703fc76ae7174ba467ecc32e727317</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5475,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T04:46:28.184073+00:00</t>
+          <t>2026-10-24T15:21:42.281783+00:00</t>
         </is>
       </c>
       <c r="F4" s="2" t="n"/>
@@ -5466,7 +5486,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>854a02a26c6f5903553e05247c002c650393714c2eb8e5e4dfbcbbb097cd17e7</t>
+          <t>2927743ae8b97cdbe399b771748d29920e5cc267678ec8c86840d17c4cce7e7d</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5511,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T04:46:28.252293+00:00</t>
+          <t>2026-10-24T15:21:42.360556+00:00</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -5506,9 +5526,429 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43d50f3d998e542a99aa57fdc557a56b0c322af7966912d64d49712ff4cc556a</t>
-        </is>
-      </c>
+          <t>95bcf7f0c3c34259e0ce01a7761b4a62315979eed6de2fbdde6d79e1cffee4a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CASE-fedce3f2-0903-44b4-bf01-f2381620d456</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>3185</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>identified</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:41.996140-04:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>(notes omitted)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>CASE-02cf4c7d-cc3c-4e9d-80e4-98ce47bdfa9f</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>3186</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>identified</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:41.996140-04:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>(notes omitted)</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CASE-68771de1-de87-4bb7-a632-f9224f3797fb</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>3187</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>identified</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:41.996140-04:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>(notes omitted)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>CASE-a51fbd0b-deb9-47e0-a569-f8ad6bc4a2e3</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>3188</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>identified</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:41.996140-04:00</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>(notes omitted)</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CASE-f3448b4d-3c36-4ff8-969c-7daf5c18d1fc</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>3189</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>identified</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:41.996140-04:00</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>(notes omitted)</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CASE-4601f1dc-42b7-4aa3-a341-3f6bd0476ebd</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>3190</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>identified</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:41.996140-04:00</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>(notes omitted)</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>CASE-631ef8fd-9bde-4839-ba44-afa1f6108743</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>3191</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>identified</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:41.996140-04:00</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>(notes omitted)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>CASE-edd7325a-96ea-4dcd-9273-a4f4ce275295</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>3192</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>identified</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:41.996140-04:00</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>(notes omitted)</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>CASE-37b7f760-fc15-41e7-af44-933a2b895c25</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>3193</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>identified</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:41.996140-04:00</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>(notes omitted)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>CASE-fedce3f2-0903-44b4-bf01-f2381620d456</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>3194</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>review_confirm</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>DEMO-REVIEWER</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:42.113206-04:00</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>(notes omitted)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>CASE-68771de1-de87-4bb7-a632-f9224f3797fb</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>3195</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>review_confirm</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>DEMO-REVIEWER</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:42.194984-04:00</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>(notes omitted)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>CASE-a51fbd0b-deb9-47e0-a569-f8ad6bc4a2e3</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>3196</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>review_confirm</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>DEMO-REVIEWER</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:42.278237-04:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>(notes omitted)</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>CASE-631ef8fd-9bde-4839-ba44-afa1f6108743</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>3197</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>review_request_evidence</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>DEMO-REVIEWER</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:42.356736-04:00</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>DEMO-REVIEWER</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>(notes omitted)</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5639,4 +6079,407 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Case reference</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Facility</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Review basis</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Latest status</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Correction / evidence reference</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Verified run</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Last evidence run</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Updated at</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CASE-631ef8fd-9bde-4839-ba44-afa1f6108743</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>RIVERBEND</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Approved rate mismatch</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Awaiting evidence</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>DEMO-REVIEWER</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>RUN-c6c77b43defc42aaa23dc71ea9270825</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:42.356736-04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>CASE-a51fbd0b-deb9-47e0-a569-f8ad6bc4a2e3</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>RIVERBEND</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Approved rate mismatch</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>RUN-c6c77b43defc42aaa23dc71ea9270825</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:42.278237-04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CASE-68771de1-de87-4bb7-a632-f9224f3797fb</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>BAYSIDE</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Approved work not in invoice extract</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>RUN-c6c77b43defc42aaa23dc71ea9270825</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:42.194984-04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CASE-fedce3f2-0903-44b4-bf01-f2381620d456</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>BAYSIDE</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Approved rate mismatch</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>RUN-c6c77b43defc42aaa23dc71ea9270825</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:42.113206-04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CASE-02cf4c7d-cc3c-4e9d-80e4-98ce47bdfa9f</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>BAYSIDE</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Approved rate mismatch</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>RUN-c6c77b43defc42aaa23dc71ea9270825</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:41.996140-04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>CASE-37b7f760-fc15-41e7-af44-933a2b895c25</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>RIVERBEND</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Time approval pending</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>RUN-c6c77b43defc42aaa23dc71ea9270825</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:41.996140-04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CASE-4601f1dc-42b7-4aa3-a341-3f6bd0476ebd</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>RIVERBEND</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Expected invoice amount mismatch</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>RUN-c6c77b43defc42aaa23dc71ea9270825</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:41.996140-04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>CASE-edd7325a-96ea-4dcd-9273-a4f4ce275295</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>RIVERBEND</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Unsupported component</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>RUN-c6c77b43defc42aaa23dc71ea9270825</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:41.996140-04:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CASE-f3448b4d-3c36-4ff8-969c-7daf5c18d1fc</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>RIVERBEND</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Approved rate mismatch</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>RUN-c6c77b43defc42aaa23dc71ea9270825</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:21:41.996140-04:00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;CShiftClarity | Fictional evaluation only | Page &amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>